--- a/src/test/resources/migracion-test/05-produccion.xlsx
+++ b/src/test/resources/migracion-test/05-produccion.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="233">
   <si>
     <t>nombre</t>
   </si>
@@ -460,6 +460,93 @@
     <t>carb_fecha_final</t>
   </si>
   <si>
+    <t>numero_elaboraciones</t>
+  </si>
+  <si>
+    <t>og_s1</t>
+  </si>
+  <si>
+    <t>vol_final_s1</t>
+  </si>
+  <si>
+    <t>hora_inicio_s1</t>
+  </si>
+  <si>
+    <t>hora_fin_s1</t>
+  </si>
+  <si>
+    <t>fecha_s2</t>
+  </si>
+  <si>
+    <t>agua_s2</t>
+  </si>
+  <si>
+    <t>og_s2</t>
+  </si>
+  <si>
+    <t>og_brix_s2</t>
+  </si>
+  <si>
+    <t>vol_final_s2</t>
+  </si>
+  <si>
+    <t>hora_inicio_s2</t>
+  </si>
+  <si>
+    <t>hora_fin_s2</t>
+  </si>
+  <si>
+    <t>nombre_receta_s2</t>
+  </si>
+  <si>
+    <t>fecha_s3</t>
+  </si>
+  <si>
+    <t>agua_s3</t>
+  </si>
+  <si>
+    <t>og_s3</t>
+  </si>
+  <si>
+    <t>og_brix_s3</t>
+  </si>
+  <si>
+    <t>vol_final_s3</t>
+  </si>
+  <si>
+    <t>hora_inicio_s3</t>
+  </si>
+  <si>
+    <t>hora_fin_s3</t>
+  </si>
+  <si>
+    <t>nombre_receta_s3</t>
+  </si>
+  <si>
+    <t>fecha_s4</t>
+  </si>
+  <si>
+    <t>agua_s4</t>
+  </si>
+  <si>
+    <t>og_s4</t>
+  </si>
+  <si>
+    <t>og_brix_s4</t>
+  </si>
+  <si>
+    <t>vol_final_s4</t>
+  </si>
+  <si>
+    <t>hora_inicio_s4</t>
+  </si>
+  <si>
+    <t>hora_fin_s4</t>
+  </si>
+  <si>
+    <t>nombre_receta_s4</t>
+  </si>
+  <si>
     <t>IPA-2024-001</t>
   </si>
   <si>
@@ -502,9 +589,6 @@
     <t>Botella 330mL</t>
   </si>
   <si>
-    <t>14.2</t>
-  </si>
-  <si>
     <t>3.5</t>
   </si>
   <si>
@@ -551,6 +635,33 @@
   </si>
   <si>
     <t>2024-05-12</t>
+  </si>
+  <si>
+    <t>1060</t>
+  </si>
+  <si>
+    <t>10.0</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>1054</t>
+  </si>
+  <si>
+    <t>9.5</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>17:30</t>
   </si>
   <si>
     <t>STT-2024-001</t>
@@ -1388,7 +1499,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP6"/>
+  <dimension ref="A1:BS6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1518,28 +1629,115 @@
       <c r="AP1" t="s" s="0">
         <v>146</v>
       </c>
+      <c r="AQ1" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="AR1" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="AS1" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="AT1" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="AU1" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="AV1" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="AW1" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="AX1" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="AY1" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="AZ1" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="BA1" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="BB1" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="BC1" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="BD1" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="BE1" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="BF1" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="BG1" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="BH1" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="BI1" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="BJ1" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="BK1" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="BL1" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="BM1" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="BN1" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="BO1" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="BP1" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="BQ1" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="BR1" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="BS1" t="s" s="0">
+        <v>175</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>15</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>21</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="H4" t="s" s="0">
         <v>25</v>
@@ -1548,251 +1746,425 @@
         <v>64</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="L4" t="s" s="0">
         <v>14</v>
       </c>
       <c r="M4" t="s" s="0">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="N4" t="s" s="0">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="O4" t="s" s="0">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="P4" t="s" s="0">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="Q4" t="s" s="0">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="R4" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="S4" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="T4" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="U4" t="s" s="0">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="V4" t="s" s="0">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="W4" t="s" s="0">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="X4" t="s" s="0">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="Y4" t="s" s="0">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="Z4" t="s" s="0">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="AA4" t="s" s="0">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="AB4" t="s" s="0">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="AC4" t="s" s="0">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="AD4" t="s" s="0">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="AE4" t="s" s="0">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="AF4" t="s" s="0">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="AG4" t="s" s="0">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="AH4" t="s" s="0">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="AI4" t="s" s="0">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="AJ4" t="s" s="0">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="AK4" t="s" s="0">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="AL4" t="s" s="0">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="AM4" t="s" s="0">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="AN4" t="s" s="0">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="AO4" t="s" s="0">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="AP4" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="AQ4" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="AR4" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AS4" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="AT4" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="AU4" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="AV4" t="s" s="0">
         <v>177</v>
+      </c>
+      <c r="AW4" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="AX4" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="AY4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AZ4" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="BA4" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="BB4" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="BC4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BD4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BE4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BF4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BG4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BH4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BI4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BJ4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BK4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BL4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BM4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BO4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BP4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BQ4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BR4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BS4" t="s" s="0">
+        <v>187</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>28</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>180</v>
+        <v>217</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>31</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="H5" t="s" s="0">
         <v>35</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>183</v>
+        <v>220</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>184</v>
+        <v>221</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="L5" t="s" s="0">
         <v>27</v>
       </c>
       <c r="M5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="N5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="O5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="P5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="Q5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="R5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="S5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="T5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="U5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="V5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="W5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="X5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="Y5" t="s" s="0">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="Z5" t="s" s="0">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="AA5" t="s" s="0">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="AB5" t="s" s="0">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="AC5" t="s" s="0">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="AD5" t="s" s="0">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="AE5" t="s" s="0">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="AF5" t="s" s="0">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="AG5" t="s" s="0">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="AH5" t="s" s="0">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="AI5" t="s" s="0">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="AJ5" t="s" s="0">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="AK5" t="s" s="0">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="AL5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="AM5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="AN5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="AO5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="AP5" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
+      </c>
+      <c r="AQ5" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="AR5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AS5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AT5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AU5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AV5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AW5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AX5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AY5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AZ5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BA5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BB5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BC5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BD5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BE5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BF5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BG5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BH5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BI5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BJ5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BK5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BL5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BM5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BN5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BO5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BP5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BQ5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BR5" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BS5" t="s" s="0">
+        <v>187</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>40</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>18</v>
@@ -1801,106 +2173,193 @@
         <v>44</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="L6" t="s" s="0">
         <v>37</v>
       </c>
       <c r="M6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="N6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="O6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="P6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="Q6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="R6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="S6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="T6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="U6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="V6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="W6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="X6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="Y6" t="s" s="0">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="Z6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="AA6" t="s" s="0">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="AB6" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="AC6" t="s" s="0">
         <v>195</v>
       </c>
-      <c r="AC6" t="s" s="0">
-        <v>167</v>
-      </c>
       <c r="AD6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="AE6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="AF6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="AG6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="AH6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="AI6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="AJ6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="AK6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="AL6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="AM6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="AN6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="AO6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="AP6" t="s" s="0">
-        <v>158</v>
+        <v>187</v>
+      </c>
+      <c r="AQ6" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="AR6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AS6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AT6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AU6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AV6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AW6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AX6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AY6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AZ6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BA6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BB6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BC6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BD6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BE6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BF6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BG6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BH6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BI6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BJ6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BK6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BL6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BM6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BN6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BO6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BP6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BQ6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BR6" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BS6" t="s" s="0">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -1929,7 +2388,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>50</v>
@@ -1943,7 +2402,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>50</v>
@@ -1957,7 +2416,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>55</v>
@@ -1971,7 +2430,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>55</v>
@@ -1985,7 +2444,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>60</v>
@@ -1999,7 +2458,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>63</v>
@@ -2013,7 +2472,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>50</v>
@@ -2027,7 +2486,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>50</v>
@@ -2041,7 +2500,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>50</v>
@@ -2055,7 +2514,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="B13" t="s" s="0">
         <v>55</v>
@@ -2069,7 +2528,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>60</v>
@@ -2083,7 +2542,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>50</v>
@@ -2097,7 +2556,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="B16" t="s" s="0">
         <v>50</v>
@@ -2111,7 +2570,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="B17" t="s" s="0">
         <v>60</v>
